--- a/TIME TABLE SAMPLE DATA/subject-continuous-rules-template.xlsx
+++ b/TIME TABLE SAMPLE DATA/subject-continuous-rules-template.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\rajas\OneDrive\Desktop\Timetable\TIME TABLE SAMPLE DATA\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ganig\Desktop\Time_Table_\TIME TABLE SAMPLE DATA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5E824300-7F88-4B2E-8D16-45EC866C06ED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{03A15049-9346-4915-98BC-2FBD73A457E1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -388,14 +388,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B3"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:B2"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="14.44140625" customWidth="1"/>
-    <col min="2" max="2" width="49.21875" customWidth="1"/>
+    <col min="1" max="1" width="14.453125" customWidth="1"/>
+    <col min="2" max="2" width="49.1796875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -403,7 +403,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A2">
         <v>11</v>
       </c>
@@ -411,14 +411,6 @@
         <v>2</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A3">
-        <v>12</v>
-      </c>
-      <c r="B3">
-        <v>2</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
